--- a/Analysis/raw data/Survey 1 clean_near complete_16.6.26.xlsx
+++ b/Analysis/raw data/Survey 1 clean_near complete_16.6.26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ranidavis/Desktop/Bats &amp; agriculture/Beneficial Bats - collaborative paper/IBRC paper analysis/IBRC beneficial bats survey response analysis/Analysis/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE22101A-DA69-8042-A82B-12DC7F989AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2C54DE-CE85-5043-9CA2-1A87CF135EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-37740" yWindow="-1960" windowWidth="36180" windowHeight="19100" xr2:uid="{A13CC812-5A33-7B48-9C68-0D1EC558A51C}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="707">
   <si>
     <t>Status</t>
   </si>
@@ -2417,6 +2417,9 @@
   </si>
   <si>
     <t>ZC &amp; HK</t>
+  </si>
+  <si>
+    <t>AMS</t>
   </si>
 </sst>
 </file>
@@ -4672,7 +4675,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="C4" s="29">
         <v>1</v>
@@ -4693,7 +4696,7 @@
         <v>438</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>63</v>
